--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="inf16" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -88,6 +88,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="17">
   <si>
     <t>sector</t>
   </si>
@@ -68,6 +68,9 @@
   <si>
     <t>нижний кластер:</t>
   </si>
+  <si>
+    <t>Year</t>
+  </si>
 </sst>
 </file>
 
@@ -76,7 +79,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +99,15 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -135,7 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -151,6 +163,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -168,6 +184,1144 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$D$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$40:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75320035180004941</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80558451044020529</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94055185443048506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$D$40:$D$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-86BD-4295-8391-1F001ABF86FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$40:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75320035180004941</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80558451044020529</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94055185443048506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$E$40:$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.8576536031471178</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80890079918421609</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79155969555065653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-86BD-4295-8391-1F001ABF86FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$F$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$40:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75320035180004941</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80558451044020529</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94055185443048506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$F$40:$F$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>9.4632036706885733E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27164901806536035</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13278607396570202</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-86BD-4295-8391-1F001ABF86FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$40:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75320035180004941</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80558451044020529</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94055185443048506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$G$40:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.30845304233506288</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46444703398099701</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.47223470956791447</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-86BD-4295-8391-1F001ABF86FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="973682783"/>
+        <c:axId val="973684031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="973682783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973684031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973684031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973682783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>157161</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="97.85546875" customWidth="1"/>
@@ -773,7 +1927,7 @@
         <v>247129.27438025735</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>14</v>
       </c>
@@ -794,7 +1948,7 @@
         <v>2.0187386386990346E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -815,11 +1969,453 @@
         <v>3.4335388058007936E-3</v>
       </c>
     </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.868819729404374E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3097084.3107878752</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4162.4721680000002</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1.4081114307645259E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2652658.7944572391</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4253.6615775199998</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2.8806641846538372E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1.8380008135386839E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2480166.278394436</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4510.0316159999993</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1.003512255644462E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.2206708220113729E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="3">
+        <f>AVERAGE(D22:D23)</f>
+        <v>3194960.8489508154</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:G28" si="2">AVERAGE(E22:E23)</f>
+        <v>4710.5211470200002</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="2"/>
+        <v>6.0062360898401829E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="2"/>
+        <v>2.9131078421489398E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D24:D25)</f>
+        <v>2566412.5364258373</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G29" si="3">AVERAGE(E24:E25)</f>
+        <v>4381.8465967599996</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="3"/>
+        <v>1.9420882201491496E-3</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="3"/>
+        <v>1.5293358177750284E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C32" s="2">
+        <f>MAX(C22:C25)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" ref="D32:G32" si="4">MAX(D22:D25)</f>
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="4"/>
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="4"/>
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="4"/>
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2">
+        <f>C22/C$32</f>
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2">
+        <f>D22/D$32</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <f>E22/E$32</f>
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <f>F22/F$32</f>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <f>G22/G$32</f>
+        <v>0.47223470956791447</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f>C23/C$32</f>
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="2">
+        <f>D23/D$32</f>
+        <v>0.94055185443048506</v>
+      </c>
+      <c r="E35" s="2">
+        <f>E23/E$32</f>
+        <v>0.79155969555065653</v>
+      </c>
+      <c r="F35" s="2">
+        <f>F23/F$32</f>
+        <v>0.13278607396570202</v>
+      </c>
+      <c r="G35" s="2">
+        <f>G23/G$32</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f>C24/C$32</f>
+        <v>0.75</v>
+      </c>
+      <c r="D36" s="2">
+        <f>D24/D$32</f>
+        <v>0.80558451044020529</v>
+      </c>
+      <c r="E36" s="2">
+        <f>E24/E$32</f>
+        <v>0.80890079918421609</v>
+      </c>
+      <c r="F36" s="2">
+        <f>F24/F$32</f>
+        <v>0.27164901806536035</v>
+      </c>
+      <c r="G36" s="2">
+        <f>G24/G$32</f>
+        <v>0.46444703398099701</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f>C25/C$32</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <f>D25/D$32</f>
+        <v>0.75320035180004941</v>
+      </c>
+      <c r="E37" s="2">
+        <f>E25/E$32</f>
+        <v>0.8576536031471178</v>
+      </c>
+      <c r="F37" s="2">
+        <f>F25/F$32</f>
+        <v>9.4632036706885733E-2</v>
+      </c>
+      <c r="G37" s="2">
+        <f>G25/G$32</f>
+        <v>0.30845304233506288</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="2">
+        <v>0.75320035180004941</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.8576536031471178</v>
+      </c>
+      <c r="F40" s="2">
+        <v>9.4632036706885733E-2</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.30845304233506288</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="2">
+        <v>0.80558451044020529</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.80890079918421609</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.27164901806536035</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.46444703398099701</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="2">
+        <v>0.94055185443048506</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.79155969555065653</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.13278607396570202</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.47223470956791447</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G13">
-    <sortCondition descending="1" ref="D2:D13"/>
+  <sortState ref="C40:G43">
+    <sortCondition ref="D40:D43"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D25">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -831,7 +2427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E22:E25">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -843,7 +2439,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F22:F25">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -855,7 +2451,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G22:G25">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -867,7 +2463,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
+  <conditionalFormatting sqref="D28:D29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -879,7 +2475,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
+  <conditionalFormatting sqref="E28:E29">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -891,7 +2487,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
+  <conditionalFormatting sqref="F28:F29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -903,7 +2499,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G28:G29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -917,5 +2513,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="18">
   <si>
     <t>sector</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>разница</t>
   </si>
 </sst>
 </file>
@@ -201,6 +204,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Растеневодство и животноводство</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -556,6 +584,60 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>ВДС</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -621,6 +703,60 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1100">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Значения</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -680,7 +816,1367 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Лесоводство и лесозаготовки</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$D$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$64:$C$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66852955180892759</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69534444026312525</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84363984930998226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$D$64:$D$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CC82-459B-BA54-B3062BF1D998}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$64:$C$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66852955180892759</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69534444026312525</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84363984930998226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$E$64:$E$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.4402945925625405</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52902112565978732</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.90671933182361841</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CC82-459B-BA54-B3062BF1D998}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$F$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$64:$C$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66852955180892759</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69534444026312525</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84363984930998226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$F$64:$F$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8493475551092914E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22280018724681394</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4040106003615581E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CC82-459B-BA54-B3062BF1D998}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$64:$C$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66852955180892759</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69534444026312525</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84363984930998226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$G$64:$G$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64910428735409798</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11320385208744876</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11460367065763803</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CC82-459B-BA54-B3062BF1D998}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="973682783"/>
+        <c:axId val="973684031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="973682783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>ВДС</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973684031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973684031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1100">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Значения</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973682783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Лесоводство и лесозаготовки</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$D$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$90:$C$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.65827404185196259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72063588438241077</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76967912664721516</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$D$90:$D$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7ADE-4E55-862E-9043ECFCD86D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$90:$C$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.65827404185196259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72063588438241077</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76967912664721516</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$E$90:$E$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.93036188524979146</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89486466263685271</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92056985015890336</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7ADE-4E55-862E-9043ECFCD86D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$F$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$90:$C$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.65827404185196259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72063588438241077</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76967912664721516</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$F$90:$F$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.38380661149699324</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58030951631362893</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61461781856355813</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7ADE-4E55-862E-9043ECFCD86D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16'!$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'inf16'!$C$90:$C$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.65827404185196259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72063588438241077</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.76967912664721516</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16'!$G$90:$G$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17205197251437845</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53699617048426662</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.8220027587306817E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7ADE-4E55-862E-9043ECFCD86D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="973682783"/>
+        <c:axId val="973684031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="973682783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>ВДС</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973684031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973684031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1100">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Значения</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973682783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -773,7 +2269,1119 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1316,6 +3924,70 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>462642</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>262617</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>7485</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>437029</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>237004</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>11488</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1609,7 +4281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="97.85546875" customWidth="1"/>
@@ -2103,29 +4775,50 @@
         <v>1.5293358177750284E-3</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3">
+        <f>D28/D29</f>
+        <v>1.2449132022244318</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" ref="E30:G30" si="4">E28/E29</f>
+        <v>1.0750082283809359</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="4"/>
+        <v>3.092669028896593</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="4"/>
+        <v>1.9048189470819483</v>
+      </c>
+    </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C32" s="2">
         <f>MAX(C22:C25)</f>
         <v>4</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" ref="D32:G32" si="4">MAX(D22:D25)</f>
+        <f t="shared" ref="D32:G32" si="5">MAX(D22:D25)</f>
         <v>3292837.3871137551</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5258.5701260400001</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0604360748915839E-2</v>
       </c>
       <c r="G32" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.9573959548935052E-3</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C33" s="7" t="s">
         <v>16</v>
       </c>
@@ -2142,95 +4835,95 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C34" s="2">
-        <f>C22/C$32</f>
+        <f t="shared" ref="C34:G37" si="6">C22/C$32</f>
         <v>0.25</v>
       </c>
       <c r="D34" s="2">
-        <f>D22/D$32</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f>E22/E$32</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F34" s="2">
-        <f>F22/F$32</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <f>G22/G$32</f>
+        <f t="shared" si="6"/>
         <v>0.47223470956791447</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C35" s="2">
-        <f>C23/C$32</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="D35" s="2">
-        <f>D23/D$32</f>
+        <f t="shared" si="6"/>
         <v>0.94055185443048506</v>
       </c>
       <c r="E35" s="2">
-        <f>E23/E$32</f>
+        <f t="shared" si="6"/>
         <v>0.79155969555065653</v>
       </c>
       <c r="F35" s="2">
-        <f>F23/F$32</f>
+        <f t="shared" si="6"/>
         <v>0.13278607396570202</v>
       </c>
       <c r="G35" s="2">
-        <f>G23/G$32</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C36" s="2">
-        <f>C24/C$32</f>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="D36" s="2">
-        <f>D24/D$32</f>
+        <f t="shared" si="6"/>
         <v>0.80558451044020529</v>
       </c>
       <c r="E36" s="2">
-        <f>E24/E$32</f>
+        <f t="shared" si="6"/>
         <v>0.80890079918421609</v>
       </c>
       <c r="F36" s="2">
-        <f>F24/F$32</f>
+        <f t="shared" si="6"/>
         <v>0.27164901806536035</v>
       </c>
       <c r="G36" s="2">
-        <f>G24/G$32</f>
+        <f t="shared" si="6"/>
         <v>0.46444703398099701</v>
       </c>
     </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C37" s="2">
-        <f>C25/C$32</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <f>D25/D$32</f>
+        <f t="shared" si="6"/>
         <v>0.75320035180004941</v>
       </c>
       <c r="E37" s="2">
-        <f>E25/E$32</f>
+        <f t="shared" si="6"/>
         <v>0.8576536031471178</v>
       </c>
       <c r="F37" s="2">
-        <f>F25/F$32</f>
+        <f t="shared" si="6"/>
         <v>9.4632036706885733E-2</v>
       </c>
       <c r="G37" s="2">
-        <f>G25/G$32</f>
+        <f t="shared" si="6"/>
         <v>0.30845304233506288</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C39" s="7" t="s">
         <v>3</v>
       </c>
@@ -2247,7 +4940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2">
         <v>0.75320035180004941</v>
       </c>
@@ -2264,7 +4957,7 @@
         <v>0.30845304233506288</v>
       </c>
     </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2">
         <v>0.80558451044020529</v>
       </c>
@@ -2281,7 +4974,7 @@
         <v>0.46444703398099701</v>
       </c>
     </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C42" s="2">
         <v>0.94055185443048506</v>
       </c>
@@ -2298,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C43" s="2">
         <v>1</v>
       </c>
@@ -2315,11 +5008,937 @@
         <v>0.47223470956791447</v>
       </c>
     </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3">
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1454.99992092</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2.7347370558508639E-4</v>
+      </c>
+      <c r="G46" s="4">
+        <v>8.7625687236728058E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3">
+        <v>149725.9222474432</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1319.2765561000001</v>
+      </c>
+      <c r="F47" s="4">
+        <v>9.5143491498901212E-3</v>
+      </c>
+      <c r="G47" s="4">
+        <v>8.6555389370039323E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2">
+        <v>4</v>
+      </c>
+      <c r="D48" s="3">
+        <v>123407.0292947656</v>
+      </c>
+      <c r="E48" s="3">
+        <v>769.72569599999997</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1.643806367093142E-3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>4.963035559098705E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3">
+        <v>118648.02708896549</v>
+      </c>
+      <c r="E49" s="3">
+        <v>640.62859736000007</v>
+      </c>
+      <c r="F49" s="4">
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G49" s="4">
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3">
+        <f>AVERAGE(D46:D47)</f>
+        <v>163601.01822824604</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" ref="E52:G52" si="7">AVERAGE(E46:E47)</f>
+        <v>1387.1382385100001</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="7"/>
+        <v>4.8939114277376039E-3</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="7"/>
+        <v>8.709053830338369E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3">
+        <f>AVERAGE(D48:D49)</f>
+        <v>121027.52819186554</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" ref="E53:G53" si="8">AVERAGE(E48:E49)</f>
+        <v>705.17714668000008</v>
+      </c>
+      <c r="F53" s="4">
+        <f t="shared" si="8"/>
+        <v>2.2173656221685406E-2</v>
+      </c>
+      <c r="G53" s="4">
+        <f t="shared" si="8"/>
+        <v>6.3045055919771584E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="3">
+        <f>D52/D53</f>
+        <v>1.3517669960910756</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" ref="E54" si="9">E52/E53</f>
+        <v>1.9670776981935643</v>
+      </c>
+      <c r="F54" s="3">
+        <f t="shared" ref="F54" si="10">F52/F53</f>
+        <v>0.22070836576565364</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" ref="G54" si="11">G52/G53</f>
+        <v>0.13814015553291181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="2">
+        <f>MAX(C46:C49)</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" ref="D56:G56" si="12">MAX(D46:D49)</f>
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="12"/>
+        <v>1454.99992092</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="12"/>
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G56" s="2">
+        <f t="shared" si="12"/>
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="2">
+        <f>C46/C$56</f>
+        <v>0.25</v>
+      </c>
+      <c r="D58" s="2">
+        <f>D46/D$56</f>
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <f>E46/E$56</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <f>F46/F$56</f>
+        <v>6.4040106003615581E-3</v>
+      </c>
+      <c r="G58" s="2">
+        <f>G46/G$56</f>
+        <v>0.11460367065763803</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f t="shared" ref="C59:C61" si="13">C47/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" ref="D59:G61" si="14">D47/D$56</f>
+        <v>0.84363984930998226</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="14"/>
+        <v>0.90671933182361841</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="14"/>
+        <v>0.22280018724681394</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="14"/>
+        <v>0.11320385208744876</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="14"/>
+        <v>0.69534444026312525</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="14"/>
+        <v>0.52902112565978732</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="14"/>
+        <v>3.8493475551092914E-2</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="14"/>
+        <v>0.64910428735409798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="14"/>
+        <v>0.66852955180892759</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="14"/>
+        <v>0.4402945925625405</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <v>0.66852955180892759</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.4402945925625405</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2">
+        <v>0.69534444026312525</v>
+      </c>
+      <c r="D65" s="2">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.52902112565978732</v>
+      </c>
+      <c r="F65" s="2">
+        <v>3.8493475551092914E-2</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.64910428735409798</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="2">
+        <v>0.84363984930998226</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.90671933182361841</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.22280018724681394</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.11320385208744876</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E67" s="2">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>6.4040106003615581E-3</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.11460367065763803</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3">
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E72" s="3">
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F72" s="4">
+        <v>7.4163848413873461E-4</v>
+      </c>
+      <c r="G72" s="4">
+        <v>3.6380912535570372E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>3</v>
+      </c>
+      <c r="D73" s="3">
+        <v>255261.79722573471</v>
+      </c>
+      <c r="E73" s="3">
+        <v>888.20773440000005</v>
+      </c>
+      <c r="F73" s="4">
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G73" s="4">
+        <v>2.863735386990569E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="2">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3">
+        <v>238996.75153477999</v>
+      </c>
+      <c r="E74" s="3">
+        <v>863.40619829999991</v>
+      </c>
+      <c r="F74" s="4">
+        <v>7.0023981897559661E-4</v>
+      </c>
+      <c r="G74" s="4">
+        <v>9.1753228267274999E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="2">
+        <v>4</v>
+      </c>
+      <c r="D75" s="3">
+        <v>218314.63160777459</v>
+      </c>
+      <c r="E75" s="3">
+        <v>897.65553599999998</v>
+      </c>
+      <c r="F75" s="4">
+        <v>4.6312642581418888E-4</v>
+      </c>
+      <c r="G75" s="4">
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="3">
+        <f>AVERAGE(D72:D73)</f>
+        <v>293454.41414568154</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" ref="E78:G78" si="15">AVERAGE(E72:E73)</f>
+        <v>926.52664817999994</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="15"/>
+        <v>9.7415229046034983E-4</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="15"/>
+        <v>1.6137722561731364E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3">
+        <f>AVERAGE(D74:D75)</f>
+        <v>228655.69157127728</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" ref="E79:G79" si="16">AVERAGE(E74:E75)</f>
+        <v>880.53086714999995</v>
+      </c>
+      <c r="F79" s="4">
+        <f t="shared" si="16"/>
+        <v>5.8168312239489277E-4</v>
+      </c>
+      <c r="G79" s="4">
+        <f t="shared" si="16"/>
+        <v>3.1252054423913846E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="3">
+        <f>D78/D79</f>
+        <v>1.2833899393849333</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" ref="E80" si="17">E78/E79</f>
+        <v>1.0522364209432813</v>
+      </c>
+      <c r="F80" s="3">
+        <f t="shared" ref="F80" si="18">F78/F79</f>
+        <v>1.6747130060256721</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" ref="G80" si="19">G78/G79</f>
+        <v>0.51637317479464306</v>
+      </c>
+    </row>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f>MAX(C72:C75)</f>
+        <v>4</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" ref="D82:G82" si="20">MAX(D72:D75)</f>
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="20"/>
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="20"/>
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G82" s="2">
+        <f t="shared" si="20"/>
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C83" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>C72/C$56</f>
+        <v>0.25</v>
+      </c>
+      <c r="D84" s="2">
+        <f>D72/D$82</f>
+        <v>1</v>
+      </c>
+      <c r="E84" s="2">
+        <f>E72/E$82</f>
+        <v>1</v>
+      </c>
+      <c r="F84" s="2">
+        <f>F72/F$82</f>
+        <v>0.61461781856355813</v>
+      </c>
+      <c r="G84" s="2">
+        <f>G72/G$82</f>
+        <v>6.8220027587306817E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f t="shared" ref="C85:G87" si="21">C73/C$56</f>
+        <v>0.75</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" ref="D85:G87" si="22">D73/D$82</f>
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="22"/>
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="22"/>
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f t="shared" si="21"/>
+        <v>0.5</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="22"/>
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="22"/>
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="22"/>
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="22"/>
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="22"/>
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="22"/>
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="22"/>
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C90" s="2">
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="2">
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="2">
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E93" s="2">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0.61461781856355813</v>
+      </c>
+      <c r="G93" s="2">
+        <v>6.8220027587306817E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="C40:G43">
-    <sortCondition ref="D40:D43"/>
+  <sortState ref="C90:G93">
+    <sortCondition ref="C90:C93"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D25">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E25">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F25">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G25">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E29">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F29">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G29">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46:D49">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -2331,7 +5950,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E46:E49">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2343,7 +5962,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F46:F49">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2355,7 +5974,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G46:G49">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2367,7 +5986,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2379,7 +5998,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2391,7 +6010,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2403,7 +6022,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2415,7 +6034,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D25">
+  <conditionalFormatting sqref="D72:D75">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2427,7 +6046,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E25">
+  <conditionalFormatting sqref="E72:E75">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2439,7 +6058,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F25">
+  <conditionalFormatting sqref="F72:F75">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2451,7 +6070,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G25">
+  <conditionalFormatting sqref="G72:G75">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2463,7 +6082,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28:D29">
+  <conditionalFormatting sqref="D78:D79">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2475,7 +6094,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:E29">
+  <conditionalFormatting sqref="E78:E79">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2487,7 +6106,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F29">
+  <conditionalFormatting sqref="F78:F79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2499,7 +6118,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G29">
+  <conditionalFormatting sqref="G78:G79">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="inf16" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
@@ -223,8 +226,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Растеневодство и животноводство</a:t>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>01</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -262,19 +267,19 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$D$39</c:f>
+              <c:f>'inf16'!$C$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Year</c:v>
+                  <c:v>0,75</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -282,7 +287,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -292,29 +297,28 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$40:$C$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.75320035180004941</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.80558451044020529</c:v>
+                  <c:v>ITcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94055185443048506</c:v>
+                  <c:v>skvozcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>trainingcosts_s</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'inf16'!$D$40:$D$43</c:f>
+              <c:f>'inf16'!$D$40:$G$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -322,184 +326,33 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75</c:v>
+                  <c:v>0.8576536031471178</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>9.4632036706885733E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.25</c:v>
+                  <c:v>0.30845304233506288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-86BD-4295-8391-1F001ABF86FE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$E$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$40:$C$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75320035180004941</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80558451044020529</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.94055185443048506</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$E$40:$E$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.8576536031471178</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80890079918421609</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.79155969555065653</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-86BD-4295-8391-1F001ABF86FE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$F$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$40:$C$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.75320035180004941</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.80558451044020529</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.94055185443048506</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$F$40:$F$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>9.4632036706885733E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.27164901806536035</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13278607396570202</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-86BD-4295-8391-1F001ABF86FE}"/>
+              <c16:uniqueId val="{00000000-19FD-4A6F-B1D6-3B18BEC02549}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$G$39</c:f>
+              <c:f>'inf16'!$C$43</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>trainingcosts_s</c:v>
+                  <c:v>1,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -517,37 +370,36 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'inf16'!$C$40:$C$43</c:f>
+              <c:f>'inf16'!$D$43:$G$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.75320035180004941</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.80558451044020529</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.94055185443048506</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$G$40:$G$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.30845304233506288</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.46444703398099701</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -558,10 +410,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-86BD-4295-8391-1F001ABF86FE}"/>
+              <c16:uniqueId val="{00000003-19FD-4A6F-B1D6-3B18BEC02549}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -573,71 +424,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="973682783"/>
-        <c:axId val="973684031"/>
-      </c:lineChart>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
       <c:catAx>
-        <c:axId val="973682783"/>
+        <c:axId val="744722240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1200">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>ВДС</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -660,12 +456,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -675,7 +468,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973684031"/>
+        <c:crossAx val="744723072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -683,7 +476,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="973684031"/>
+        <c:axId val="744723072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -703,60 +496,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Значения</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -773,12 +512,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -788,7 +524,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973682783"/>
+        <c:crossAx val="744722240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -801,7 +537,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -816,12 +552,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -903,8 +636,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Лесоводство и лесозаготовки</a:t>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>02</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -942,19 +677,19 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$D$39</c:f>
+              <c:f>'inf16'!$C$64</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Year</c:v>
+                  <c:v>0,67</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -962,7 +697,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -972,29 +707,28 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$64:$C$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.66852955180892759</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69534444026312525</c:v>
+                  <c:v>ITcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.84363984930998226</c:v>
+                  <c:v>skvozcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>trainingcosts_s</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'inf16'!$D$64:$D$67</c:f>
+              <c:f>'inf16'!$D$64:$G$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1002,85 +736,10 @@
                   <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0.4402945925625405</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CC82-459B-BA54-B3062BF1D998}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$E$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$64:$C$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.66852955180892759</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.69534444026312525</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.84363984930998226</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$E$64:$E$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.4402945925625405</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.52902112565978732</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.90671933182361841</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -1088,98 +747,22 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-CC82-459B-BA54-B3062BF1D998}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$F$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$64:$C$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.66852955180892759</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.69534444026312525</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.84363984930998226</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$F$64:$F$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.8493475551092914E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.22280018724681394</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.4040106003615581E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-CC82-459B-BA54-B3062BF1D998}"/>
+              <c16:uniqueId val="{00000000-C870-4EC4-B01C-907EDE755F4C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$G$39</c:f>
+              <c:f>'inf16'!$C$67</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>trainingcosts_s</c:v>
+                  <c:v>1,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1197,40 +780,39 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'inf16'!$C$64:$C$67</c:f>
+              <c:f>'inf16'!$D$67:$G$67</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.66852955180892759</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69534444026312525</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.84363984930998226</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$G$64:$G$67</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.64910428735409798</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11320385208744876</c:v>
+                  <c:v>6.4040106003615581E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.11460367065763803</c:v>
@@ -1238,10 +820,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-CC82-459B-BA54-B3062BF1D998}"/>
+              <c16:uniqueId val="{00000003-C870-4EC4-B01C-907EDE755F4C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1253,71 +834,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="973682783"/>
-        <c:axId val="973684031"/>
-      </c:lineChart>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
       <c:catAx>
-        <c:axId val="973682783"/>
+        <c:axId val="744722240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1200">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>ВДС</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1340,12 +866,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1355,7 +878,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973684031"/>
+        <c:crossAx val="744723072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1363,7 +886,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="973684031"/>
+        <c:axId val="744723072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1383,60 +906,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Значения</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1453,12 +922,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1468,7 +934,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973682783"/>
+        <c:crossAx val="744722240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1481,7 +947,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1496,12 +962,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1583,8 +1046,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Лесоводство и лесозаготовки</a:t>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>02</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1622,19 +1087,19 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$D$39</c:f>
+              <c:f>'inf16'!$C$90</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Year</c:v>
+                  <c:v>0,66</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1642,7 +1107,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1652,29 +1117,28 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$90:$C$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.65827404185196259</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.72063588438241077</c:v>
+                  <c:v>ITcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.76967912664721516</c:v>
+                  <c:v>skvozcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>trainingcosts_s</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'inf16'!$D$90:$D$93</c:f>
+              <c:f>'inf16'!$D$90:$G$90</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1682,85 +1146,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.93036188524979146</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7ADE-4E55-862E-9043ECFCD86D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$E$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$90:$C$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.65827404185196259</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.72063588438241077</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.76967912664721516</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$E$90:$E$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.93036188524979146</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.89486466263685271</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.92056985015890336</c:v>
+                  <c:v>0.38380661149699324</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -1768,98 +1157,22 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7ADE-4E55-862E-9043ECFCD86D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'inf16'!$F$39</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'inf16'!$C$90:$C$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.65827404185196259</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.72063588438241077</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.76967912664721516</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$F$90:$F$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.38380661149699324</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.58030951631362893</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.61461781856355813</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7ADE-4E55-862E-9043ECFCD86D}"/>
+              <c16:uniqueId val="{00000000-048D-47D1-AE0F-426145B94BD5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$G$39</c:f>
+              <c:f>'inf16'!$C$93</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>trainingcosts_s</c:v>
+                  <c:v>1,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1877,40 +1190,39 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>'inf16'!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'inf16'!$C$90:$C$93</c:f>
+              <c:f>'inf16'!$D$93:$G$93</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.65827404185196259</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.72063588438241077</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.76967912664721516</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'inf16'!$G$90:$G$93</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.17205197251437845</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.53699617048426662</c:v>
+                  <c:v>0.61461781856355813</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>6.8220027587306817E-2</c:v>
@@ -1918,10 +1230,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7ADE-4E55-862E-9043ECFCD86D}"/>
+              <c16:uniqueId val="{00000003-048D-47D1-AE0F-426145B94BD5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1933,71 +1244,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="973682783"/>
-        <c:axId val="973684031"/>
-      </c:lineChart>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
       <c:catAx>
-        <c:axId val="973682783"/>
+        <c:axId val="744722240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1200">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>ВДС</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2020,12 +1276,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2035,7 +1288,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973684031"/>
+        <c:crossAx val="744723072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2043,7 +1296,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="973684031"/>
+        <c:axId val="744723072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2063,60 +1316,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Значения</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2133,12 +1332,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2148,7 +1344,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973682783"/>
+        <c:crossAx val="744722240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2161,7 +1357,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -2176,12 +1372,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -2350,7 +1543,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2458,11 +1651,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2473,11 +1661,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2509,9 +1692,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2567,22 +1747,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2687,8 +1868,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2820,19 +2001,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2866,7 +2048,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2974,11 +2156,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2989,11 +2166,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3025,9 +2197,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3083,22 +2252,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3203,8 +2373,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3336,19 +2506,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3382,7 +2553,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3490,11 +2661,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3505,11 +2671,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3541,9 +2702,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3599,22 +2757,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3719,8 +2878,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3852,19 +3011,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3901,21 +3061,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>157161</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>560294</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>72801</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>34926</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Диаграмма 3"/>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3931,20 +3093,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>462642</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>176893</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>262617</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>7485</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>301723</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>40529</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -3964,19 +3126,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>437029</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>237004</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>11488</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>138436</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>40529</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvPr id="8" name="Диаграмма 7"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -3994,6 +3156,106 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Original"/>
+      <sheetName val="Only best"/>
+      <sheetName val="Best|Worst"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E89" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="C90">
+            <v>0.60541707637600206</v>
+          </cell>
+          <cell r="D90">
+            <v>0.75</v>
+          </cell>
+          <cell r="E90">
+            <v>1</v>
+          </cell>
+          <cell r="F90">
+            <v>0.80661939562538798</v>
+          </cell>
+          <cell r="G90">
+            <v>0.45477225885659545</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="C91">
+            <v>0.62826451624711255</v>
+          </cell>
+          <cell r="D91">
+            <v>1</v>
+          </cell>
+          <cell r="E91">
+            <v>0.7323973572762863</v>
+          </cell>
+          <cell r="F91">
+            <v>0.9611546957323327</v>
+          </cell>
+          <cell r="G91">
+            <v>0.83771179639168136</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0.78924387345553881</v>
+          </cell>
+          <cell r="D92">
+            <v>0.5</v>
+          </cell>
+          <cell r="E92">
+            <v>0.90624842311195075</v>
+          </cell>
+          <cell r="F92">
+            <v>1</v>
+          </cell>
+          <cell r="G92">
+            <v>0.67809276193519175</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93">
+            <v>1</v>
+          </cell>
+          <cell r="D93">
+            <v>0.25</v>
+          </cell>
+          <cell r="E93">
+            <v>0.89882061387652312</v>
+          </cell>
+          <cell r="F93">
+            <v>0.17795127025264079</v>
+          </cell>
+          <cell r="G93">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4941,7 +4203,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <v>0.75320035180004941</v>
       </c>
       <c r="D40" s="2">
@@ -4958,7 +4220,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>0.80558451044020529</v>
       </c>
       <c r="D41" s="2">
@@ -4975,7 +4237,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <v>0.94055185443048506</v>
       </c>
       <c r="D42" s="2">
@@ -4992,7 +4254,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>1</v>
       </c>
       <c r="D43" s="2">
@@ -5308,7 +4570,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="2">
+      <c r="C64" s="3">
         <v>0.66852955180892759</v>
       </c>
       <c r="D64" s="2">
@@ -5325,7 +4587,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C65" s="2">
+      <c r="C65" s="3">
         <v>0.69534444026312525</v>
       </c>
       <c r="D65" s="2">
@@ -5342,7 +4604,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C66" s="2">
+      <c r="C66" s="3">
         <v>0.84363984930998226</v>
       </c>
       <c r="D66" s="2">
@@ -5359,7 +4621,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <v>1</v>
       </c>
       <c r="D67" s="2">
@@ -5593,7 +4855,7 @@
     </row>
     <row r="85" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C85" s="2">
-        <f t="shared" ref="C85:G87" si="21">C73/C$56</f>
+        <f t="shared" ref="C85:C87" si="21">C73/C$56</f>
         <v>0.75</v>
       </c>
       <c r="D85" s="2">
@@ -5675,7 +4937,7 @@
       </c>
     </row>
     <row r="90" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C90" s="2">
+      <c r="C90" s="3">
         <v>0.65827404185196259</v>
       </c>
       <c r="D90" s="2">
@@ -5692,7 +4954,7 @@
       </c>
     </row>
     <row r="91" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="2">
+      <c r="C91" s="3">
         <v>0.72063588438241077</v>
       </c>
       <c r="D91" s="2">
@@ -5709,7 +4971,7 @@
       </c>
     </row>
     <row r="92" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C92" s="2">
+      <c r="C92" s="3">
         <v>0.76967912664721516</v>
       </c>
       <c r="D92" s="2">
@@ -5726,7 +4988,7 @@
       </c>
     </row>
     <row r="93" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C93" s="2">
+      <c r="C93" s="3">
         <v>1</v>
       </c>
       <c r="D93" s="2">

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -14,9 +14,6 @@
   <sheets>
     <sheet name="inf16" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
@@ -1049,7 +1046,7 @@
               <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>02</a:t>
+              <a:t>03</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3156,106 +3153,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Original"/>
-      <sheetName val="Only best"/>
-      <sheetName val="Best|Worst"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>ITcosts_s</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>skvozcosts_s</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>trainingcosts_s</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="C90">
-            <v>0.60541707637600206</v>
-          </cell>
-          <cell r="D90">
-            <v>0.75</v>
-          </cell>
-          <cell r="E90">
-            <v>1</v>
-          </cell>
-          <cell r="F90">
-            <v>0.80661939562538798</v>
-          </cell>
-          <cell r="G90">
-            <v>0.45477225885659545</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="C91">
-            <v>0.62826451624711255</v>
-          </cell>
-          <cell r="D91">
-            <v>1</v>
-          </cell>
-          <cell r="E91">
-            <v>0.7323973572762863</v>
-          </cell>
-          <cell r="F91">
-            <v>0.9611546957323327</v>
-          </cell>
-          <cell r="G91">
-            <v>0.83771179639168136</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="C92">
-            <v>0.78924387345553881</v>
-          </cell>
-          <cell r="D92">
-            <v>0.5</v>
-          </cell>
-          <cell r="E92">
-            <v>0.90624842311195075</v>
-          </cell>
-          <cell r="F92">
-            <v>1</v>
-          </cell>
-          <cell r="G92">
-            <v>0.67809276193519175</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -74,6 +74,15 @@
   <si>
     <t>разница</t>
   </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
+  </si>
+  <si>
+    <t>сред</t>
+  </si>
 </sst>
 </file>
 
@@ -82,12 +91,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -148,11 +165,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -167,8 +184,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1092,7 +1118,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$C$90</c:f>
+              <c:f>'inf16'!$C$88</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1135,7 +1161,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'inf16'!$D$90:$G$90</c:f>
+              <c:f>'inf16'!$D$88:$G$88</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1165,7 +1191,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'inf16'!$C$93</c:f>
+              <c:f>'inf16'!$C$91</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1208,7 +1234,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'inf16'!$D$93:$G$93</c:f>
+              <c:f>'inf16'!$D$91:$G$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3058,16 +3084,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>560294</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>369794</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>158920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>72801</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>34926</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>488438</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>104199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3090,16 +3116,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>21029</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>181841</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>301723</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>40529</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>145859</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>127120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3122,16 +3148,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>13607</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>377289</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>43295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>138436</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>40529</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>502119</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>179074</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3440,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="97.85546875" customWidth="1"/>
@@ -3758,7 +3784,7 @@
         <v>247129.27438025735</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>14</v>
       </c>
@@ -3779,7 +3805,7 @@
         <v>2.0187386386990346E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>15</v>
       </c>
@@ -3800,7 +3826,7 @@
         <v>3.4335388058007936E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -3822,8 +3848,15 @@
       <c r="G22" s="4">
         <v>1.868819729404374E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I22" s="2"/>
+      <c r="J22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -3845,8 +3878,17 @@
       <c r="G23" s="4">
         <v>3.9573959548935052E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.92014669347994649</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.63822884618079689</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -3868,8 +3910,17 @@
       <c r="G24" s="4">
         <v>1.8380008135386839E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0.14289442569325148</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1.2602577684922229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -3891,8 +3942,30 @@
       <c r="G25" s="4">
         <v>1.2206708220113729E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.46180103499922054</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1.3356237696952309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="10">
+        <f>AVERAGE(J23:J25)</f>
+        <v>0.50828071805747277</v>
+      </c>
+      <c r="K27" s="10">
+        <f>AVERAGE(K23:K25)</f>
+        <v>1.0780367947894167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
@@ -3913,7 +3986,7 @@
         <v>2.9131078421489398E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -3934,7 +4007,7 @@
         <v>1.5293358177750284E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>17</v>
       </c>
@@ -3955,7 +4028,7 @@
         <v>1.9048189470819483</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C32" s="2">
         <f>MAX(C22:C25)</f>
         <v>4</v>
@@ -4236,7 +4309,7 @@
         <v>4.963035559098705E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
@@ -4259,7 +4332,7 @@
         <v>7.645975624855611E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
         <v>14</v>
       </c>
@@ -4280,7 +4353,7 @@
         <v>8.709053830338369E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B53" s="6" t="s">
         <v>15</v>
       </c>
@@ -4301,7 +4374,7 @@
         <v>6.3045055919771584E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B54" s="6" t="s">
         <v>17</v>
       </c>
@@ -4322,7 +4395,7 @@
         <v>0.13814015553291181</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C56" s="2">
         <f>MAX(C46:C49)</f>
         <v>4</v>
@@ -4344,7 +4417,7 @@
         <v>7.645975624855611E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C57" s="7" t="s">
         <v>16</v>
       </c>
@@ -4360,8 +4433,15 @@
       <c r="G57" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J57" s="2"/>
+      <c r="K57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C58" s="2">
         <f>C46/C$56</f>
         <v>0.25</v>
@@ -4382,8 +4462,19 @@
         <f>G46/G$56</f>
         <v>0.11460367065763803</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J58" s="7">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>0.92014669347994649</v>
+      </c>
+      <c r="L58" s="3">
+        <f>0.5*(D40*E40+E40*F40+F40*G40+G40*D40)</f>
+        <v>0.63822884618079689</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2">
         <f t="shared" ref="C59:C61" si="13">C47/C$56</f>
         <v>0.5</v>
@@ -4405,7 +4496,7 @@
         <v>0.11320385208744876</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="2">
         <f t="shared" si="13"/>
         <v>1</v>
@@ -4427,7 +4518,7 @@
         <v>0.64910428735409798</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2">
         <f t="shared" si="13"/>
         <v>0.75</v>
@@ -4449,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="7" t="s">
         <v>3</v>
       </c>
@@ -4466,7 +4557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C64" s="3">
         <v>0.66852955180892759</v>
       </c>
@@ -4534,6 +4625,52 @@
         <v>0.11460367065763803</v>
       </c>
     </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3">
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E70" s="3">
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F70" s="4">
+        <v>7.4163848413873461E-4</v>
+      </c>
+      <c r="G70" s="4">
+        <v>3.6380912535570372E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+      <c r="D71" s="3">
+        <v>255261.79722573471</v>
+      </c>
+      <c r="E71" s="3">
+        <v>888.20773440000005</v>
+      </c>
+      <c r="F71" s="4">
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G71" s="4">
+        <v>2.863735386990569E-3</v>
+      </c>
+    </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
@@ -4542,19 +4679,19 @@
         <v>12</v>
       </c>
       <c r="C72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" s="3">
-        <v>331647.0310656284</v>
+        <v>238996.75153477999</v>
       </c>
       <c r="E72" s="3">
-        <v>964.84556195999994</v>
+        <v>863.40619829999991</v>
       </c>
       <c r="F72" s="4">
-        <v>7.4163848413873461E-4</v>
+        <v>7.0023981897559661E-4</v>
       </c>
       <c r="G72" s="4">
-        <v>3.6380912535570372E-4</v>
+        <v>9.1753228267274999E-4</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4565,344 +4702,338 @@
         <v>12</v>
       </c>
       <c r="C73" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" s="3">
-        <v>255261.79722573471</v>
+        <v>218314.63160777459</v>
       </c>
       <c r="E73" s="3">
-        <v>888.20773440000005</v>
+        <v>897.65553599999998</v>
       </c>
       <c r="F73" s="4">
-        <v>1.2066660967819649E-3</v>
+        <v>4.6312642581418888E-4</v>
       </c>
       <c r="G73" s="4">
-        <v>2.863735386990569E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" s="2">
-        <v>2</v>
-      </c>
-      <c r="D74" s="3">
-        <v>238996.75153477999</v>
-      </c>
-      <c r="E74" s="3">
-        <v>863.40619829999991</v>
-      </c>
-      <c r="F74" s="4">
-        <v>7.0023981897559661E-4</v>
-      </c>
-      <c r="G74" s="4">
-        <v>9.1753228267274999E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="2">
-        <v>4</v>
-      </c>
-      <c r="D75" s="3">
-        <v>218314.63160777459</v>
-      </c>
-      <c r="E75" s="3">
-        <v>897.65553599999998</v>
-      </c>
-      <c r="F75" s="4">
-        <v>4.6312642581418888E-4</v>
-      </c>
-      <c r="G75" s="4">
         <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="3">
+        <f>AVERAGE(D70:D71)</f>
+        <v>293454.41414568154</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" ref="E76:G76" si="15">AVERAGE(E70:E71)</f>
+        <v>926.52664817999994</v>
+      </c>
+      <c r="F76" s="4">
+        <f t="shared" si="15"/>
+        <v>9.7415229046034983E-4</v>
+      </c>
+      <c r="G76" s="4">
+        <f t="shared" si="15"/>
+        <v>1.6137722561731364E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3">
+        <f>AVERAGE(D72:D73)</f>
+        <v>228655.69157127728</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" ref="E77:G77" si="16">AVERAGE(E72:E73)</f>
+        <v>880.53086714999995</v>
+      </c>
+      <c r="F77" s="4">
+        <f t="shared" si="16"/>
+        <v>5.8168312239489277E-4</v>
+      </c>
+      <c r="G77" s="4">
+        <f t="shared" si="16"/>
+        <v>3.1252054423913846E-3</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B78" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D78" s="3">
-        <f>AVERAGE(D72:D73)</f>
-        <v>293454.41414568154</v>
+        <f>D76/D77</f>
+        <v>1.2833899393849333</v>
       </c>
       <c r="E78" s="3">
-        <f t="shared" ref="E78:G78" si="15">AVERAGE(E72:E73)</f>
-        <v>926.52664817999994</v>
-      </c>
-      <c r="F78" s="4">
-        <f t="shared" si="15"/>
-        <v>9.7415229046034983E-4</v>
-      </c>
-      <c r="G78" s="4">
-        <f t="shared" si="15"/>
-        <v>1.6137722561731364E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B79" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" s="3">
-        <f>AVERAGE(D74:D75)</f>
-        <v>228655.69157127728</v>
-      </c>
-      <c r="E79" s="3">
-        <f t="shared" ref="E79:G79" si="16">AVERAGE(E74:E75)</f>
-        <v>880.53086714999995</v>
-      </c>
-      <c r="F79" s="4">
-        <f t="shared" si="16"/>
-        <v>5.8168312239489277E-4</v>
-      </c>
-      <c r="G79" s="4">
-        <f t="shared" si="16"/>
-        <v>3.1252054423913846E-3</v>
+        <f t="shared" ref="E78" si="17">E76/E77</f>
+        <v>1.0522364209432813</v>
+      </c>
+      <c r="F78" s="3">
+        <f t="shared" ref="F78" si="18">F76/F77</f>
+        <v>1.6747130060256721</v>
+      </c>
+      <c r="G78" s="3">
+        <f t="shared" ref="G78" si="19">G76/G77</f>
+        <v>0.51637317479464306</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B80" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D80" s="3">
-        <f>D78/D79</f>
-        <v>1.2833899393849333</v>
-      </c>
-      <c r="E80" s="3">
-        <f t="shared" ref="E80" si="17">E78/E79</f>
-        <v>1.0522364209432813</v>
-      </c>
-      <c r="F80" s="3">
-        <f t="shared" ref="F80" si="18">F78/F79</f>
-        <v>1.6747130060256721</v>
-      </c>
-      <c r="G80" s="3">
-        <f t="shared" ref="G80" si="19">G78/G79</f>
-        <v>0.51637317479464306</v>
-      </c>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C82" s="2">
-        <f>MAX(C72:C75)</f>
+      <c r="C80" s="2">
+        <f>MAX(C70:C73)</f>
         <v>4</v>
       </c>
-      <c r="D82" s="2">
-        <f t="shared" ref="D82:G82" si="20">MAX(D72:D75)</f>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:G80" si="20">MAX(D70:D73)</f>
         <v>331647.0310656284</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E80" s="2">
         <f t="shared" si="20"/>
         <v>964.84556195999994</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F80" s="2">
         <f t="shared" si="20"/>
         <v>1.2066660967819649E-3</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G80" s="2">
         <f t="shared" si="20"/>
         <v>5.3328786021100191E-3</v>
       </c>
     </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C83" s="7" t="s">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D81" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="J81" s="2"/>
+      <c r="K81" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f>C70/C$56</f>
+        <v>0.25</v>
+      </c>
+      <c r="D82" s="2">
+        <f>D70/D$80</f>
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
+        <f>E70/E$80</f>
+        <v>1</v>
+      </c>
+      <c r="F82" s="2">
+        <f>F70/F$80</f>
+        <v>0.61461781856355813</v>
+      </c>
+      <c r="G82" s="2">
+        <f>G70/G$80</f>
+        <v>6.8220027587306817E-2</v>
+      </c>
+      <c r="J82" s="7">
+        <v>2</v>
+      </c>
+      <c r="K82" s="3">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.14289442569325148</v>
+      </c>
+      <c r="L82" s="3">
+        <f>0.5*(D64*E64+E64*F64+F64*G64+G64*D64)</f>
+        <v>1.2602577684922229</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f>C71/C$56</f>
+        <v>0.75</v>
+      </c>
+      <c r="D83" s="2">
+        <f>D71/D$80</f>
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="E83" s="2">
+        <f>E71/E$80</f>
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F83" s="2">
+        <f>F71/F$80</f>
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <f>G71/G$80</f>
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C84" s="2">
         <f>C72/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D84" s="2">
+        <f>D72/D$80</f>
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="E84" s="2">
+        <f>E72/E$80</f>
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F84" s="2">
+        <f>F72/F$80</f>
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G84" s="2">
+        <f>G72/G$80</f>
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f>C73/C$56</f>
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <f>D73/D$80</f>
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="E85" s="2">
+        <f>E73/E$80</f>
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F85" s="2">
+        <f>F73/F$80</f>
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G85" s="2">
+        <f>G73/G$80</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="3">
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G88" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="3">
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G89" s="2">
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="3">
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
         <v>0.25</v>
       </c>
-      <c r="D84" s="2">
-        <f>D72/D$82</f>
+      <c r="E91" s="2">
         <v>1</v>
       </c>
-      <c r="E84" s="2">
-        <f>E72/E$82</f>
-        <v>1</v>
-      </c>
-      <c r="F84" s="2">
-        <f>F72/F$82</f>
+      <c r="F91" s="2">
         <v>0.61461781856355813</v>
       </c>
-      <c r="G84" s="2">
-        <f>G72/G$82</f>
+      <c r="G91" s="2">
         <v>6.8220027587306817E-2</v>
       </c>
     </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C85" s="2">
-        <f t="shared" ref="C85:C87" si="21">C73/C$56</f>
-        <v>0.75</v>
-      </c>
-      <c r="D85" s="2">
-        <f t="shared" ref="D85:G87" si="22">D73/D$82</f>
-        <v>0.76967912664721516</v>
-      </c>
-      <c r="E85" s="2">
-        <f t="shared" si="22"/>
-        <v>0.92056985015890336</v>
-      </c>
-      <c r="F85" s="2">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="G85" s="2">
-        <f t="shared" si="22"/>
-        <v>0.53699617048426662</v>
-      </c>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C86" s="2">
-        <f t="shared" si="21"/>
-        <v>0.5</v>
-      </c>
-      <c r="D86" s="2">
-        <f t="shared" si="22"/>
-        <v>0.72063588438241077</v>
-      </c>
-      <c r="E86" s="2">
-        <f t="shared" si="22"/>
-        <v>0.89486466263685271</v>
-      </c>
-      <c r="F86" s="2">
-        <f t="shared" si="22"/>
-        <v>0.58030951631362893</v>
-      </c>
-      <c r="G86" s="2">
-        <f t="shared" si="22"/>
-        <v>0.17205197251437845</v>
-      </c>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C87" s="2">
-        <f t="shared" si="21"/>
-        <v>1</v>
-      </c>
-      <c r="D87" s="2">
-        <f t="shared" si="22"/>
-        <v>0.65827404185196259</v>
-      </c>
-      <c r="E87" s="2">
-        <f t="shared" si="22"/>
-        <v>0.93036188524979146</v>
-      </c>
-      <c r="F87" s="2">
-        <f t="shared" si="22"/>
-        <v>0.38380661149699324</v>
-      </c>
-      <c r="G87" s="2">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C89" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C90" s="3">
-        <v>0.65827404185196259</v>
-      </c>
-      <c r="D90" s="2">
-        <v>1</v>
-      </c>
-      <c r="E90" s="2">
-        <v>0.93036188524979146</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0.38380661149699324</v>
-      </c>
-      <c r="G90" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C91" s="3">
-        <v>0.72063588438241077</v>
-      </c>
-      <c r="D91" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E91" s="2">
-        <v>0.89486466263685271</v>
-      </c>
-      <c r="F91" s="2">
-        <v>0.58030951631362893</v>
-      </c>
-      <c r="G91" s="2">
-        <v>0.17205197251437845</v>
-      </c>
-    </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C92" s="3">
-        <v>0.76967912664721516</v>
-      </c>
-      <c r="D92" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E92" s="2">
-        <v>0.92056985015890336</v>
-      </c>
-      <c r="F92" s="2">
-        <v>1</v>
-      </c>
-      <c r="G92" s="2">
-        <v>0.53699617048426662</v>
-      </c>
-    </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C93" s="3">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E93" s="2">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2">
-        <v>0.61461781856355813</v>
-      </c>
-      <c r="G93" s="2">
-        <v>6.8220027587306817E-2</v>
+    <row r="105" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+      <c r="K105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="7">
+        <v>2</v>
+      </c>
+      <c r="K106" s="3">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>0.46180103499922054</v>
+      </c>
+      <c r="L106" s="3">
+        <f>0.5*(D88*E88+E88*F88+F88*G88+G88*D88)</f>
+        <v>1.3356237696952309</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="C90:G93">
+  <sortState ref="C88:G91">
     <sortCondition ref="C90:C93"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
@@ -5193,7 +5324,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D72:D75">
+  <conditionalFormatting sqref="D70:D73">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5205,7 +5336,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72:E75">
+  <conditionalFormatting sqref="E70:E73">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -5217,7 +5348,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F72:F75">
+  <conditionalFormatting sqref="F70:F73">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -5229,7 +5360,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G72:G75">
+  <conditionalFormatting sqref="G70:G73">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5241,7 +5372,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D78:D79">
+  <conditionalFormatting sqref="D76:D77">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5253,7 +5384,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E79">
+  <conditionalFormatting sqref="E76:E77">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5265,7 +5396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F78:F79">
+  <conditionalFormatting sqref="F76:F77">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5277,7 +5408,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G78:G79">
+  <conditionalFormatting sqref="G76:G77">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="inf16" sheetId="1" r:id="rId1"/>
@@ -4832,19 +4832,19 @@
         <v>0.25</v>
       </c>
       <c r="D82" s="2">
-        <f>D70/D$80</f>
+        <f t="shared" ref="D82:G85" si="21">D70/D$80</f>
         <v>1</v>
       </c>
       <c r="E82" s="2">
-        <f>E70/E$80</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F82" s="2">
-        <f>F70/F$80</f>
+        <f t="shared" si="21"/>
         <v>0.61461781856355813</v>
       </c>
       <c r="G82" s="2">
-        <f>G70/G$80</f>
+        <f t="shared" si="21"/>
         <v>6.8220027587306817E-2</v>
       </c>
       <c r="J82" s="7">
@@ -4865,19 +4865,19 @@
         <v>0.75</v>
       </c>
       <c r="D83" s="2">
-        <f>D71/D$80</f>
+        <f t="shared" si="21"/>
         <v>0.76967912664721516</v>
       </c>
       <c r="E83" s="2">
-        <f>E71/E$80</f>
+        <f t="shared" si="21"/>
         <v>0.92056985015890336</v>
       </c>
       <c r="F83" s="2">
-        <f>F71/F$80</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G83" s="2">
-        <f>G71/G$80</f>
+        <f t="shared" si="21"/>
         <v>0.53699617048426662</v>
       </c>
     </row>
@@ -4887,19 +4887,19 @@
         <v>0.5</v>
       </c>
       <c r="D84" s="2">
-        <f>D72/D$80</f>
+        <f t="shared" si="21"/>
         <v>0.72063588438241077</v>
       </c>
       <c r="E84" s="2">
-        <f>E72/E$80</f>
+        <f t="shared" si="21"/>
         <v>0.89486466263685271</v>
       </c>
       <c r="F84" s="2">
-        <f>F72/F$80</f>
+        <f t="shared" si="21"/>
         <v>0.58030951631362893</v>
       </c>
       <c r="G84" s="2">
-        <f>G72/G$80</f>
+        <f t="shared" si="21"/>
         <v>0.17205197251437845</v>
       </c>
     </row>
@@ -4909,19 +4909,19 @@
         <v>1</v>
       </c>
       <c r="D85" s="2">
-        <f>D73/D$80</f>
+        <f t="shared" si="21"/>
         <v>0.65827404185196259</v>
       </c>
       <c r="E85" s="2">
-        <f>E73/E$80</f>
+        <f t="shared" si="21"/>
         <v>0.93036188524979146</v>
       </c>
       <c r="F85" s="2">
-        <f>F73/F$80</f>
+        <f t="shared" si="21"/>
         <v>0.38380661149699324</v>
       </c>
       <c r="G85" s="2">
-        <f>G73/G$80</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>

--- a/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/agro sector (VDS_s) 0.xlsx
@@ -9,17 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="inf16" sheetId="1" r:id="rId1"/>
+    <sheet name="inf16 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -1445,6 +1449,1212 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>01</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,75</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$40:$G$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.8576536031471178</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.4632036706885733E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30845304233506288</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6F4C-409A-9C08-EE29BBCF603C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$43</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$43:$G$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.47223470956791447</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6F4C-409A-9C08-EE29BBCF603C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>02</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,67</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$64:$G$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.4402945925625405</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E23B-4305-99D7-2B2695F840A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$67</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$67:$G$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4040106003615581E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11460367065763803</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E23B-4305-99D7-2B2695F840A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>03</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$88</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,66</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$88:$G$88</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.93036188524979146</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.38380661149699324</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-75A3-4221-B95C-71C80331F316}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$C$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'inf16 (2)'!$E$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'inf16 (2)'!$E$91:$G$91</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.61461781856355813</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.8220027587306817E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-75A3-4221-B95C-71C80331F316}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1565,6 +2775,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -2576,6 +3906,1521 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3179,6 +6024,190 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>467590</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>86591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>411925</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>207819</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>121228</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>152154</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>167988</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>277092</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>221426</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>185306</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet1 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="42">
+          <cell r="E42" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>0.53195397442833625</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>0.4341128768543896</v>
+          </cell>
+          <cell r="G43">
+            <v>0.96268324181002174</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>0.74071957251902487</v>
+          </cell>
+          <cell r="E44">
+            <v>0.81436789578742097</v>
+          </cell>
+          <cell r="F44">
+            <v>1</v>
+          </cell>
+          <cell r="G44">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>0.88899585107146872</v>
+          </cell>
+          <cell r="E45">
+            <v>0.3732928962109599</v>
+          </cell>
+          <cell r="F45">
+            <v>0.78623653793827153</v>
+          </cell>
+          <cell r="G45">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>1</v>
+          </cell>
+          <cell r="E46">
+            <v>0.37449706271284755</v>
+          </cell>
+          <cell r="F46">
+            <v>0.59247665944601891</v>
+          </cell>
+          <cell r="G46">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5424,4 +8453,1963 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="97.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.868819729404374E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3097084.3107878752</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4162.4721680000002</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.4081114307645259E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2652658.7944572391</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4253.6615775199998</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.8806641846538372E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.8380008135386839E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2480166.278394436</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4510.0316159999993</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.003512255644462E-3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.2206708220113729E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D6" s="3">
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E6" s="3">
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F6" s="4">
+        <v>7.4163848413873461E-4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3.6380912535570372E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="3">
+        <v>255261.79722573471</v>
+      </c>
+      <c r="E7" s="3">
+        <v>888.20773440000005</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2.863735386990569E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="3">
+        <v>238996.75153477999</v>
+      </c>
+      <c r="E8" s="3">
+        <v>863.40619829999991</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7.0023981897559661E-4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>9.1753228267274999E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D9" s="3">
+        <v>218314.63160777459</v>
+      </c>
+      <c r="E9" s="3">
+        <v>897.65553599999998</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.6312642581418888E-4</v>
+      </c>
+      <c r="G9" s="4">
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="3">
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1454.99992092</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2.7347370558508639E-4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>8.7625687236728058E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="3">
+        <v>149725.9222474432</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1319.2765561000001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>9.5143491498901212E-3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>8.6555389370039323E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="3">
+        <v>123407.0292947656</v>
+      </c>
+      <c r="E12" s="3">
+        <v>769.72569599999997</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.643806367093142E-3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>4.963035559098705E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="3">
+        <v>118648.02708896549</v>
+      </c>
+      <c r="E13" s="3">
+        <v>640.62859736000007</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>247129.27438025735</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>2018275.9331741116</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>3339.6314639866664</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>2.974158866816561E-3</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>2.0187386386990346E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>171094.74599712962</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>990.94875077999995</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>9.2164169239392999E-3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>3.4335388058007936E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.868819729404374E-3</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3097084.3107878752</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4162.4721680000002</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1.4081114307645259E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>3.9573959548935052E-3</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.92014669347994649</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.63822884618079689</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2652658.7944572391</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4253.6615775199998</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2.8806641846538372E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1.8380008135386839E-3</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0.14289442569325148</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1.2602577684922229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2480166.278394436</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4510.0316159999993</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1.003512255644462E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1.2206708220113729E-3</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.46180103499922054</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1.3356237696952309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="10">
+        <f>AVERAGE(J23:J25)</f>
+        <v>0.50828071805747277</v>
+      </c>
+      <c r="K27" s="10">
+        <f>AVERAGE(K23:K25)</f>
+        <v>1.0780367947894167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="3">
+        <f>AVERAGE(D22:D23)</f>
+        <v>3194960.8489508154</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:G28" si="2">AVERAGE(E22:E23)</f>
+        <v>4710.5211470200002</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="2"/>
+        <v>6.0062360898401829E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="2"/>
+        <v>2.9131078421489398E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D24:D25)</f>
+        <v>2566412.5364258373</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G29" si="3">AVERAGE(E24:E25)</f>
+        <v>4381.8465967599996</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="3"/>
+        <v>1.9420882201491496E-3</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="3"/>
+        <v>1.5293358177750284E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3">
+        <f>D28/D29</f>
+        <v>1.2449132022244318</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" ref="E30:G30" si="4">E28/E29</f>
+        <v>1.0750082283809359</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="4"/>
+        <v>3.092669028896593</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="4"/>
+        <v>1.9048189470819483</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="2">
+        <f>MAX(C22:C25)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" ref="D32:G32" si="5">MAX(D22:D25)</f>
+        <v>3292837.3871137551</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="5"/>
+        <v>5258.5701260400001</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="5"/>
+        <v>1.0604360748915839E-2</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="5"/>
+        <v>3.9573959548935052E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2">
+        <f t="shared" ref="C34:G37" si="6">C22/C$32</f>
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <f t="shared" si="6"/>
+        <v>0.47223470956791447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="6"/>
+        <v>0.94055185443048506</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="6"/>
+        <v>0.79155969555065653</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="6"/>
+        <v>0.13278607396570202</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f t="shared" si="6"/>
+        <v>0.75</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="6"/>
+        <v>0.80558451044020529</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="6"/>
+        <v>0.80890079918421609</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="6"/>
+        <v>0.27164901806536035</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="6"/>
+        <v>0.46444703398099701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="6"/>
+        <v>0.75320035180004941</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="6"/>
+        <v>0.8576536031471178</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="6"/>
+        <v>9.4632036706885733E-2</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="6"/>
+        <v>0.30845304233506288</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="3">
+        <v>0.75320035180004941</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.8576536031471178</v>
+      </c>
+      <c r="F40" s="2">
+        <v>9.4632036706885733E-2</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.30845304233506288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="3">
+        <v>0.80558451044020529</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.80890079918421609</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.27164901806536035</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.46444703398099701</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="3">
+        <v>0.94055185443048506</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.79155969555065653</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.13278607396570202</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.47223470956791447</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3">
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1454.99992092</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2.7347370558508639E-4</v>
+      </c>
+      <c r="G46" s="4">
+        <v>8.7625687236728058E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3">
+        <v>149725.9222474432</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1319.2765561000001</v>
+      </c>
+      <c r="F47" s="4">
+        <v>9.5143491498901212E-3</v>
+      </c>
+      <c r="G47" s="4">
+        <v>8.6555389370039323E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2">
+        <v>4</v>
+      </c>
+      <c r="D48" s="3">
+        <v>123407.0292947656</v>
+      </c>
+      <c r="E48" s="3">
+        <v>769.72569599999997</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1.643806367093142E-3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>4.963035559098705E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3">
+        <v>118648.02708896549</v>
+      </c>
+      <c r="E49" s="3">
+        <v>640.62859736000007</v>
+      </c>
+      <c r="F49" s="4">
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G49" s="4">
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="3">
+        <f>AVERAGE(D46:D47)</f>
+        <v>163601.01822824604</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" ref="E52:G52" si="7">AVERAGE(E46:E47)</f>
+        <v>1387.1382385100001</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="7"/>
+        <v>4.8939114277376039E-3</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="7"/>
+        <v>8.709053830338369E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3">
+        <f>AVERAGE(D48:D49)</f>
+        <v>121027.52819186554</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" ref="E53:G53" si="8">AVERAGE(E48:E49)</f>
+        <v>705.17714668000008</v>
+      </c>
+      <c r="F53" s="4">
+        <f t="shared" si="8"/>
+        <v>2.2173656221685406E-2</v>
+      </c>
+      <c r="G53" s="4">
+        <f t="shared" si="8"/>
+        <v>6.3045055919771584E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="3">
+        <f>D52/D53</f>
+        <v>1.3517669960910756</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" ref="E54:G54" si="9">E52/E53</f>
+        <v>1.9670776981935643</v>
+      </c>
+      <c r="F54" s="3">
+        <f t="shared" si="9"/>
+        <v>0.22070836576565364</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="9"/>
+        <v>0.13814015553291181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C56" s="2">
+        <f>MAX(C46:C49)</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" ref="D56:G56" si="10">MAX(D46:D49)</f>
+        <v>177476.11420904889</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="10"/>
+        <v>1454.99992092</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="10"/>
+        <v>4.2703506076277667E-2</v>
+      </c>
+      <c r="G56" s="2">
+        <f t="shared" si="10"/>
+        <v>7.645975624855611E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="2">
+        <f>C46/C$56</f>
+        <v>0.25</v>
+      </c>
+      <c r="D58" s="2">
+        <f>D46/D$56</f>
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <f>E46/E$56</f>
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
+        <f>F46/F$56</f>
+        <v>6.4040106003615581E-3</v>
+      </c>
+      <c r="G58" s="2">
+        <f>G46/G$56</f>
+        <v>0.11460367065763803</v>
+      </c>
+      <c r="J58" s="7">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3">
+        <f>0.5*(D43*E43+E43*F43+F43*G43+G43*D43)</f>
+        <v>0.92014669347994649</v>
+      </c>
+      <c r="L58" s="3">
+        <f>0.5*(D40*E40+E40*F40+F40*G40+G40*D40)</f>
+        <v>0.63822884618079689</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f t="shared" ref="C59:G61" si="11">C47/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D59" s="2">
+        <f t="shared" si="11"/>
+        <v>0.84363984930998226</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="11"/>
+        <v>0.90671933182361841</v>
+      </c>
+      <c r="F59" s="2">
+        <f t="shared" si="11"/>
+        <v>0.22280018724681394</v>
+      </c>
+      <c r="G59" s="2">
+        <f t="shared" si="11"/>
+        <v>0.11320385208744876</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="11"/>
+        <v>0.69534444026312525</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="11"/>
+        <v>0.52902112565978732</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="11"/>
+        <v>3.8493475551092914E-2</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="11"/>
+        <v>0.64910428735409798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="11"/>
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="11"/>
+        <v>0.66852955180892759</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="11"/>
+        <v>0.4402945925625405</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="3">
+        <v>0.66852955180892759</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.4402945925625405</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="3">
+        <v>0.69534444026312525</v>
+      </c>
+      <c r="D65" s="2">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.52902112565978732</v>
+      </c>
+      <c r="F65" s="2">
+        <v>3.8493475551092914E-2</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.64910428735409798</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="3">
+        <v>0.84363984930998226</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.90671933182361841</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.22280018724681394</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.11320385208744876</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E67" s="2">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2">
+        <v>6.4040106003615581E-3</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.11460367065763803</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3">
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E70" s="3">
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F70" s="4">
+        <v>7.4163848413873461E-4</v>
+      </c>
+      <c r="G70" s="4">
+        <v>3.6380912535570372E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2">
+        <v>3</v>
+      </c>
+      <c r="D71" s="3">
+        <v>255261.79722573471</v>
+      </c>
+      <c r="E71" s="3">
+        <v>888.20773440000005</v>
+      </c>
+      <c r="F71" s="4">
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G71" s="4">
+        <v>2.863735386990569E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2">
+        <v>2</v>
+      </c>
+      <c r="D72" s="3">
+        <v>238996.75153477999</v>
+      </c>
+      <c r="E72" s="3">
+        <v>863.40619829999991</v>
+      </c>
+      <c r="F72" s="4">
+        <v>7.0023981897559661E-4</v>
+      </c>
+      <c r="G72" s="4">
+        <v>9.1753228267274999E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2">
+        <v>4</v>
+      </c>
+      <c r="D73" s="3">
+        <v>218314.63160777459</v>
+      </c>
+      <c r="E73" s="3">
+        <v>897.65553599999998</v>
+      </c>
+      <c r="F73" s="4">
+        <v>4.6312642581418888E-4</v>
+      </c>
+      <c r="G73" s="4">
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="3">
+        <f>AVERAGE(D70:D71)</f>
+        <v>293454.41414568154</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" ref="E76:G76" si="12">AVERAGE(E70:E71)</f>
+        <v>926.52664817999994</v>
+      </c>
+      <c r="F76" s="4">
+        <f t="shared" si="12"/>
+        <v>9.7415229046034983E-4</v>
+      </c>
+      <c r="G76" s="4">
+        <f t="shared" si="12"/>
+        <v>1.6137722561731364E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3">
+        <f>AVERAGE(D72:D73)</f>
+        <v>228655.69157127728</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" ref="E77:G77" si="13">AVERAGE(E72:E73)</f>
+        <v>880.53086714999995</v>
+      </c>
+      <c r="F77" s="4">
+        <f t="shared" si="13"/>
+        <v>5.8168312239489277E-4</v>
+      </c>
+      <c r="G77" s="4">
+        <f t="shared" si="13"/>
+        <v>3.1252054423913846E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3">
+        <f>D76/D77</f>
+        <v>1.2833899393849333</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" ref="E78:G78" si="14">E76/E77</f>
+        <v>1.0522364209432813</v>
+      </c>
+      <c r="F78" s="3">
+        <f t="shared" si="14"/>
+        <v>1.6747130060256721</v>
+      </c>
+      <c r="G78" s="3">
+        <f t="shared" si="14"/>
+        <v>0.51637317479464306</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C80" s="2">
+        <f>MAX(C70:C73)</f>
+        <v>4</v>
+      </c>
+      <c r="D80" s="2">
+        <f t="shared" ref="D80:G80" si="15">MAX(D70:D73)</f>
+        <v>331647.0310656284</v>
+      </c>
+      <c r="E80" s="2">
+        <f t="shared" si="15"/>
+        <v>964.84556195999994</v>
+      </c>
+      <c r="F80" s="2">
+        <f t="shared" si="15"/>
+        <v>1.2066660967819649E-3</v>
+      </c>
+      <c r="G80" s="2">
+        <f t="shared" si="15"/>
+        <v>5.3328786021100191E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="2"/>
+      <c r="K81" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C82" s="2">
+        <f>C70/C$56</f>
+        <v>0.25</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" ref="D82:G85" si="16">D70/D$80</f>
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="F82" s="2">
+        <f t="shared" si="16"/>
+        <v>0.61461781856355813</v>
+      </c>
+      <c r="G82" s="2">
+        <f t="shared" si="16"/>
+        <v>6.8220027587306817E-2</v>
+      </c>
+      <c r="J82" s="7">
+        <v>2</v>
+      </c>
+      <c r="K82" s="3">
+        <f>0.5*(D67*E67+E67*F67+F67*G67+G67*D67)</f>
+        <v>0.14289442569325148</v>
+      </c>
+      <c r="L82" s="3">
+        <f>0.5*(D64*E64+E64*F64+F64*G64+G64*D64)</f>
+        <v>1.2602577684922229</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C83" s="2">
+        <f>C71/C$56</f>
+        <v>0.75</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" si="16"/>
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="16"/>
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F83" s="2">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <f t="shared" si="16"/>
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>C72/C$56</f>
+        <v>0.5</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" si="16"/>
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="16"/>
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="16"/>
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="16"/>
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="2">
+        <f>C73/C$56</f>
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <f t="shared" si="16"/>
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="E85" s="2">
+        <f t="shared" si="16"/>
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F85" s="2">
+        <f t="shared" si="16"/>
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G85" s="2">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="3">
+        <v>0.65827404185196259</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.93036188524979146</v>
+      </c>
+      <c r="F88" s="2">
+        <v>0.38380661149699324</v>
+      </c>
+      <c r="G88" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="3">
+        <v>0.72063588438241077</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.89486466263685271</v>
+      </c>
+      <c r="F89" s="2">
+        <v>0.58030951631362893</v>
+      </c>
+      <c r="G89" s="2">
+        <v>0.17205197251437845</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C90" s="3">
+        <v>0.76967912664721516</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0.92056985015890336</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.53699617048426662</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E91" s="2">
+        <v>1</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.61461781856355813</v>
+      </c>
+      <c r="G91" s="2">
+        <v>6.8220027587306817E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+      <c r="K105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="7">
+        <v>2</v>
+      </c>
+      <c r="K106" s="3">
+        <f>0.5*(D91*E91+E91*F91+F91*G91+G91*D91)</f>
+        <v>0.46180103499922054</v>
+      </c>
+      <c r="L106" s="3">
+        <f>0.5*(D88*E88+E88*F88+F88*G88+G88*D88)</f>
+        <v>1.3356237696952309</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D25">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E25">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F25">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G25">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E29">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F29">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G29">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D46:D49">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E46:E49">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46:F49">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G46:G49">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52:D53">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E52:E53">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52:F53">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G52:G53">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D70:D73">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70:E73">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F70:F73">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G70:G73">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76:D77">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E76:E77">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F76:F77">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G76:G77">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>